--- a/survey_templates/049_soccer_coach_evaluation_survey--survey_templates.xlsx
+++ b/survey_templates/049_soccer_coach_evaluation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>coach_satisfaction</t>
+          <t>coach_satisfaction_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>coach satisfaction</t>
+          <t>Coach Satisfaction 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>overall_satisfaction_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>overall satisfaction</t>
+          <t>Overall Satisfaction 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>feedback_from_coach</t>
+          <t>feedback_from_coach_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feedback from coach</t>
+          <t>Feedback From Coach 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>feedback_from_athlete_parents</t>
+          <t>feedback_from_athlete_parents_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feedback from athlete parents</t>
+          <t>Feedback From Athlete Parents 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -963,7 +963,7 @@
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1464,7 +1464,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>coach_satisfaction_choices</t>
+          <t>coach_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>coach_satisfaction_choices</t>
+          <t>coach_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1532,7 +1532,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>feedback_from_coach_choices</t>
+          <t>feedback_from_coach_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>feedback_from_coach_choices</t>
+          <t>feedback_from_coach_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1600,7 +1600,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>feedback_from_athlete_parents_choices</t>
+          <t>feedback_from_athlete_parents_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>feedback_from_athlete_parents_choices</t>
+          <t>feedback_from_athlete_parents_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
